--- a/results/momentum_failcodes_2026-10-06.xlsx
+++ b/results/momentum_failcodes_2026-10-06.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A270"/>
+  <dimension ref="A1:A265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,1869 +440,1834 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BZFD</t>
+          <t>AAON</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AAON</t>
+          <t>BOT</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AIIA</t>
+          <t>ABSI</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ABSI</t>
+          <t>ATOM</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FUFU</t>
+          <t>CURX</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AMBA</t>
+          <t>ABXL</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CHSCO</t>
+          <t>AZUL</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ACU</t>
+          <t>DLXY</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GNLN</t>
+          <t>ACLS</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ATII</t>
+          <t>BTTC</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CRVO</t>
+          <t>DUKRW</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ADMA</t>
+          <t>ADI</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HTLM</t>
+          <t>CRD</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AVO</t>
+          <t>ADMA</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ELLA</t>
+          <t>CRNT</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ADPT</t>
+          <t>GCL</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>RGC</t>
+          <t>ADPT</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CRUS</t>
+          <t>KBSX</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>AEHL</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AEHL</t>
+          <t>DMRC</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AEIS</t>
+          <t>MACI</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>HWKN</t>
+          <t>DUOT</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>GSRF</t>
+          <t>MDAI</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AGEN</t>
+          <t>AEIS</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ICHR</t>
+          <t>EMPD</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>INAB</t>
+          <t>AFRI</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AIIR</t>
+          <t>EVCM</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>INDV</t>
+          <t>AHG</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>KFII</t>
+          <t>HBANL</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>IQMX</t>
+          <t>AIB</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>NAUT</t>
+          <t>HYPR</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ALMR</t>
+          <t>AIIR</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>IRMD</t>
+          <t>INEO</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>NSLRL</t>
+          <t>IQMX</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ALNT</t>
+          <t>ALLT</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>LAB</t>
+          <t>ITRN</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>NTWK</t>
+          <t>ALNT</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AMPH</t>
+          <t>MAZE</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>MAZE</t>
+          <t>MIND</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>OPTX</t>
+          <t>AMBR</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AMPL</t>
+          <t>NMAD</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>OXLCM</t>
+          <t>NTRSO</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AMRX</t>
+          <t>AMPH</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MKSI</t>
+          <t>POWL</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>PDSB</t>
+          <t>AMPL</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ANGI</t>
+          <t>QUIK</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>NEON</t>
+          <t>AMRX</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>PMTR</t>
+          <t>RYAAY</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AOUT</t>
+          <t>ANDG</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>PWRL</t>
+          <t>SNWV</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ARAY</t>
+          <t>STRL</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SLMT</t>
+          <t>ATKR</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>PXS</t>
+          <t>TLN</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ARW</t>
+          <t>AVAT</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>TLN</t>
+          <t>ZSQR</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>RELL</t>
+          <t>AVPT</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ASPS</t>
+          <t>AVX</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>VERU</t>
+          <t>BATRA</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ZSQR</t>
+          <t>BBCP</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ATKR</t>
+          <t>BCAL</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SOTK</t>
+          <t>BELFB</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ATLCL</t>
+          <t>BNR</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SXTP</t>
+          <t>BOW</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AUUD</t>
+          <t>BPRE</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>THEO</t>
+          <t>BSVN</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AVPT</t>
+          <t>BTBD</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>WCCB</t>
+          <t>BZUN</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AZTA</t>
+          <t>CBAT</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>BCML</t>
+          <t>CD</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>BCTX</t>
+          <t>CDNS</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>BKHA</t>
+          <t>CELU</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>BLRK</t>
+          <t>CEVA</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>BNC</t>
+          <t>CFFI</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>BPRE</t>
+          <t>CGNT</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>BSVN</t>
+          <t>CGNX</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>BTBD</t>
+          <t>CHAD</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>BTTC</t>
+          <t>CHSCL</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>BWMN</t>
+          <t>CLMB</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>BZUN</t>
+          <t>CNXN</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>CAMT</t>
+          <t>CR</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>CDNA</t>
+          <t>CRAI</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>CDNS</t>
+          <t>CTKB</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>CELU</t>
+          <t>CVCO</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>CVLT</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>CFFI</t>
+          <t>CWBC</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>CHAD</t>
+          <t>DDI</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>CHEF</t>
+          <t>DDOG</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>CHSCL</t>
+          <t>DIOD</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>CLMB</t>
+          <t>DSGR</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>COHU</t>
+          <t>DSGX</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>CORT</t>
+          <t>DXPE</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>COSM</t>
+          <t>EGBN</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>EGHT</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>CRSR</t>
+          <t>ELMT</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>EMBC</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>CSTL</t>
+          <t>ENGS</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>CTKB</t>
+          <t>ENTG</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>CVLT</t>
+          <t>EUDA</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>CWBC</t>
+          <t>FAST</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>CYRX</t>
+          <t>FBLA</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>FEIM</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>DMAC</t>
+          <t>FFIV</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>DMRC</t>
+          <t>FIRY</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>DOCU</t>
+          <t>FLEX</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>DSGR</t>
+          <t>FMAO</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>DSGX</t>
+          <t>FOSL</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>DTST</t>
+          <t>FRHC</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>EEIQ</t>
+          <t>FROG</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>EXEL</t>
+          <t>FSBW</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>FBLA</t>
+          <t>FTRE</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>FEAM</t>
+          <t>FWDI</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>GCT</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>FIRY</t>
+          <t>GRDX</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>FLGT</t>
+          <t>HBIO</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>FNRN</t>
+          <t>HCM</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>FORM</t>
+          <t>HQI</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>FRHC</t>
+          <t>HQWWW</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>FTRE</t>
+          <t>HWKN</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>GDYN</t>
+          <t>IESC</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>GH</t>
+          <t>INKT</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>GRAL</t>
+          <t>IOSP</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>GSAT</t>
+          <t>IRDM</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>HBIO</t>
+          <t>JOYY</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>HIMX</t>
+          <t>JWEL</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>HLP</t>
+          <t>KFII</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>HSTM</t>
+          <t>KMRK</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>HTFL</t>
+          <t>KMTS</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>IDAI</t>
+          <t>KOD</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>KOPN</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>IMPPP</t>
+          <t>LCUT</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>INCR</t>
+          <t>LECO</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>INKT</t>
+          <t>LEDS</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>IOSP</t>
+          <t>LGND</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>IPGP</t>
+          <t>LIND</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>LINK</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>JAKK</t>
+          <t>LITS</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>LKFT</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>JOYY</t>
+          <t>LOPE</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>JWEL</t>
+          <t>LSBK</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>KAZR</t>
+          <t>LSCC</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>KCHV</t>
+          <t>LTRX</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>KFFB</t>
+          <t>MAR</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>KMTS</t>
+          <t>MCHPP</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>KOSS</t>
+          <t>MGNI</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>KRNT</t>
+          <t>MGRC</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>MKTX</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>LAFA</t>
+          <t>MSGY</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>LAUR</t>
+          <t>MTLS</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>LECO</t>
+          <t>MTSI</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>LGND</t>
+          <t>MXL</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>LIND</t>
+          <t>NATH</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>LINK</t>
+          <t>NCPL</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>LKFT</t>
+          <t>NDSN</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>LSBK</t>
+          <t>NICE</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>LSCC</t>
+          <t>NKSH</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>MANE</t>
+          <t>NOVT</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>MATH</t>
+          <t>NTAP</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>MBINM</t>
+          <t>NTCT</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>MKTW</t>
+          <t>NTNX</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>MLAB</t>
+          <t>NTRP</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>MNTK</t>
+          <t>NTWK</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>MPWR</t>
+          <t>NVEC</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>MRVI</t>
+          <t>NXPI</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>MSGM</t>
+          <t>OCC</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>MTSI</t>
+          <t>OESX</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>NAKA</t>
+          <t>ONC</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>NATH</t>
+          <t>OPRT</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>NCPL</t>
+          <t>OPRX</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>NDRA</t>
+          <t>OPTX</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>NDSN</t>
+          <t>OSPN</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>NHPBP</t>
+          <t>OTAI</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>NTCT</t>
+          <t>OUST</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>NTRA</t>
+          <t>PDFS</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>NTRP</t>
+          <t>PKOH</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>NTSK</t>
+          <t>PLXS</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>NUTX</t>
+          <t>PMVP</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>NVEC</t>
+          <t>PPIH</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>OCTV</t>
+          <t>PRCH</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>ODD</t>
+          <t>PS</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>OLLI</t>
+          <t>PSIG</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>OPRT</t>
+          <t>PSIX</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>OPRX</t>
+          <t>PUBM</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>OSPN</t>
+          <t>PWP</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>OSUR</t>
+          <t>PXS</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>OTAI</t>
+          <t>QMCO</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>OXLCZ</t>
+          <t>QSI</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>PAYO</t>
+          <t>RBKB</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>PAYS</t>
+          <t>RCBC</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>PDFS</t>
+          <t>RDVT</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>PKOH</t>
+          <t>RDWR</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>PLUN</t>
+          <t>RFAI</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>PLXS</t>
+          <t>RMBS</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>PPIH</t>
+          <t>RVMD</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>PPLI</t>
+          <t>RWAYL</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>PS</t>
+          <t>SBC</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>SBET</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>QLYS</t>
+          <t>SCSC</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>QNBC</t>
+          <t>SGC</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>QSEA</t>
+          <t>SHLS</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>QTRX</t>
+          <t>SHMD</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>RCEL</t>
+          <t>SILC</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>RCMT</t>
+          <t>SIMO</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>RDWR</t>
+          <t>SITM</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>REFR</t>
+          <t>SKYA</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>RFAI</t>
+          <t>SMMT</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>RILYG</t>
+          <t>SMTC</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>RUSHB</t>
+          <t>SNPS</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>RVSB</t>
+          <t>SOTK</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>SAMG</t>
+          <t>SPOK</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>SANM</t>
+          <t>SSTI</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>SAX</t>
+          <t>STRC</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>SBC</t>
+          <t>STRD</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>SCSC</t>
+          <t>STRK</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>SCYX</t>
+          <t>SUIG</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>SEER</t>
+          <t>SUJA</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>SGC</t>
+          <t>SUNB</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>SIGA</t>
+          <t>SVCO</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>SILC</t>
+          <t>TAOX</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>SIMO</t>
+          <t>TENB</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>SINT</t>
+          <t>TITN</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>SITM</t>
+          <t>TLSA</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>SLAB</t>
+          <t>TP</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>SLGL</t>
+          <t>TRNI</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>SPSC</t>
+          <t>TRNS</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>SRZN</t>
+          <t>USDEW</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>SSYS</t>
+          <t>VAI</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>STRC</t>
+          <t>WCCB</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>STRD</t>
+          <t>WLTH</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>STRF</t>
+          <t>XFLH</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>STRK</t>
+          <t>XMTR</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>SUIG</t>
+          <t>XXI</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>SVIA</t>
+          <t>KLIC</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>SVRN</t>
+          <t>VCTR</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>SWBI</t>
+          <t>COHU</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>SWKHL</t>
+          <t>CRVO</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>TAOX</t>
+          <t>ASYS</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>TONT</t>
+          <t>ICHR</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>TRNS</t>
+          <t>NVMI</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>TWAV</t>
+          <t>SYNA</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>VALU</t>
+          <t>CBNK</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>VIR</t>
+          <t>MSGM</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>WLTH</t>
+          <t>QLYS</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>XFLH</t>
+          <t>KRNT</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>XMTR</t>
+          <t>ODD</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>XRPNU</t>
+          <t>IMMP</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>LFCR</t>
+          <t>REBN</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>DLXY</t>
+          <t>III</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>IMMP</t>
+          <t>INAB</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>NVMI</t>
+          <t>BIRD</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>VICR</t>
+          <t>SLGL</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>BTLN</t>
+          <t>NAUT</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>QSI</t>
+          <t>SANG</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>FOSL</t>
+          <t>PAHC</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>STKE</t>
+          <t>RELL</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>SYNA</t>
+          <t>IMOS</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>TJGC</t>
+          <t>BTLN</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>ENTG</t>
+          <t>FEAM</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>KLIC</t>
+          <t>PAYS</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>SSTI</t>
+          <t>STKE</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>CD</t>
+          <t>OCG</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>ACLS</t>
+          <t>LFCR</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>OCC</t>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="inlineStr">
-        <is>
-          <t>MASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>ASYS</t>
-        </is>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="inlineStr">
-        <is>
-          <t>SANG</t>
-        </is>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="inlineStr">
-        <is>
-          <t>PMVP</t>
-        </is>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" t="inlineStr">
-        <is>
-          <t>REBN</t>
+          <t>MKSI</t>
         </is>
       </c>
     </row>
